--- a/assets/constructions/examples/ctd_grinding_wheel.xlsx
+++ b/assets/constructions/examples/ctd_grinding_wheel.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AG6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,11 +569,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6 200x100x76 25А F54 H 10 V 35 кл.2 П/О-3 чертеж 226000 АА W-16 ГОСТ Р 52781-07</t>
+          <t>5 200x32x76 25А F90 M 6 V 50 кл.2 чертеж 185000 выт 125*16 ГОСТ Р 52781-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -589,14 +614,14 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="H2" t="n">
         <v>76</v>
@@ -608,16 +633,16 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>F54</t>
+          <t>F90</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -625,7 +650,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -645,11 +670,22 @@
           <t>чертеж</t>
         </is>
       </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12 80x8x13 63С F150 M 7 V 35 кл.3 чертеж 121000 ГОСТ Р 52781-07</t>
+          <t>1 80x20x20 64С F60 K 7 V 35 кл.3 ГОСТ Р 52781-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -665,31 +701,31 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>80</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>63C</t>
+          <t>64C</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>F150</t>
+          <t>F60</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>K</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -718,14 +754,25 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>чертеж</t>
+          <t>https://www.abrasives.ru/</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1 750x20x305 25А F60 O 6 V 50 кл.2 ГОСТ Р 52781-07</t>
+          <t>1 500x16x305 25А F60 J 6 V 50 кл.2 ГОСТ Р 52781-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -745,10 +792,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H4" t="n">
         <v>305</v>
@@ -765,7 +812,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>J</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -797,11 +844,22 @@
           <t>https://www.abrasives.ru/</t>
         </is>
       </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1 175x6x32 25А F60 J 6 V 50 кл.2 ГОСТ Р 52781-07</t>
+          <t>1 32x20x6 25А F40 P 6 V 50 кл.2 ГОСТ Р 52781-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -821,14 +879,14 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>175</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
         <v>6</v>
       </c>
-      <c r="H5" t="n">
-        <v>32</v>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>25A</t>
@@ -836,12 +894,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>F60</t>
+          <t>F40</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>P</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -873,11 +931,22 @@
           <t>https://www.abrasives.ru/</t>
         </is>
       </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1 32x40x10 25А F60 O 6 V 50 кл.2 ГОСТ Р 52781-07</t>
+          <t>1 40x25x13 25А F90 L 6 V 50 кл.2 ГОСТ Р 52781-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -897,13 +966,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -912,12 +981,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>F60</t>
+          <t>F90</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -949,6 +1018,17 @@
           <t>https://www.abrasives.ru/</t>
         </is>
       </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
